--- a/artfynd/A 41952-2026 artfynd.xlsx
+++ b/artfynd/A 41952-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ28"/>
+  <dimension ref="A1:AZ72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -884,32 +884,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134964204</v>
+        <v>137404838</v>
       </c>
       <c r="B4" t="n">
-        <v>92241</v>
+        <v>92601</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454387</v>
+        <v>454448</v>
       </c>
       <c r="R4" t="n">
-        <v>6753992</v>
+        <v>6754167</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,12 +949,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,62 +979,62 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Caspar Ström</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134964204</t>
+          <t>https://artportalen.se/Sighting/137404838</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122406658</v>
+        <v>134964204</v>
       </c>
       <c r="B5" t="n">
-        <v>79327</v>
+        <v>92241</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långsisdammen, Långsisdammen, Dlr</t>
+          <t>Svarttjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454390</v>
+        <v>454387</v>
       </c>
       <c r="R5" t="n">
-        <v>6754454</v>
+        <v>6753992</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,22 +1061,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:44</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11:44</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,24 +1081,24 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122406658</t>
+          <t>https://artportalen.se/Sighting/134964204</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122407328</v>
+        <v>122406658</v>
       </c>
       <c r="B6" t="n">
         <v>79327</v>
@@ -1133,13 +1133,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454488</v>
+        <v>454390</v>
       </c>
       <c r="R6" t="n">
-        <v>6754361</v>
+        <v>6754454</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,24 +1193,24 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122407328</t>
+          <t>https://artportalen.se/Sighting/122406658</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122408531</v>
+        <v>122407328</v>
       </c>
       <c r="B7" t="n">
         <v>79327</v>
@@ -1241,17 +1241,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svarttjärnsberget, Svarttjärnsberget, Dlr</t>
+          <t>Långsisdammen, Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454354</v>
+        <v>454488</v>
       </c>
       <c r="R7" t="n">
-        <v>6754279</v>
+        <v>6754361</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1305,24 +1305,24 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122408531</t>
+          <t>https://artportalen.se/Sighting/122407328</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122408664</v>
+        <v>122408531</v>
       </c>
       <c r="B8" t="n">
         <v>79327</v>
@@ -1353,17 +1353,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långsisdammen, Långsisdammen, Dlr</t>
+          <t>Svarttjärnsberget, Svarttjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454418</v>
+        <v>454354</v>
       </c>
       <c r="R8" t="n">
-        <v>6754374</v>
+        <v>6754279</v>
       </c>
       <c r="S8" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1417,24 +1417,24 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122408664</t>
+          <t>https://artportalen.se/Sighting/122408531</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122408874</v>
+        <v>122408664</v>
       </c>
       <c r="B9" t="n">
         <v>79327</v>
@@ -1465,17 +1465,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långsisdammen, Dlr</t>
+          <t>Långsisdammen, Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454455</v>
+        <v>454418</v>
       </c>
       <c r="R9" t="n">
-        <v>6754359</v>
+        <v>6754374</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1502,9 +1502,19 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1519,24 +1529,24 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122408874</t>
+          <t>https://artportalen.se/Sighting/122408664</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122410040</v>
+        <v>122408874</v>
       </c>
       <c r="B10" t="n">
         <v>79327</v>
@@ -1567,17 +1577,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Svarttjärnsberget, Svarttjärnsberget, Dlr</t>
+          <t>Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454489</v>
+        <v>454455</v>
       </c>
       <c r="R10" t="n">
-        <v>6754150</v>
+        <v>6754359</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1604,19 +1614,9 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-01</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>14:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1631,24 +1631,24 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122410040</t>
+          <t>https://artportalen.se/Sighting/122408874</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122410090</v>
+        <v>122410040</v>
       </c>
       <c r="B11" t="n">
         <v>79327</v>
@@ -1679,17 +1679,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Långsisdammen, Dlr</t>
+          <t>Svarttjärnsberget, Svarttjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454474</v>
+        <v>454489</v>
       </c>
       <c r="R11" t="n">
-        <v>6754072</v>
+        <v>6754150</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1716,9 +1716,19 @@
           <t>2025-02-01</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1733,27 +1743,27 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122410090</t>
+          <t>https://artportalen.se/Sighting/122410040</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134955967</v>
+        <v>122410090</v>
       </c>
       <c r="B12" t="n">
-        <v>79411</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1781,17 +1791,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Svarttjärnsberget, Dlr</t>
+          <t>Långsisdammen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454264</v>
+        <v>454474</v>
       </c>
       <c r="R12" t="n">
-        <v>6754018</v>
+        <v>6754072</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1815,12 +1825,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-02-01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-02-01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1835,24 +1845,24 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Via Caspar Ström</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134955967</t>
+          <t>https://artportalen.se/Sighting/122410090</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134964622</v>
+        <v>134955967</v>
       </c>
       <c r="B13" t="n">
         <v>79411</v>
@@ -1887,10 +1897,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454352</v>
+        <v>454264</v>
       </c>
       <c r="R13" t="n">
-        <v>6753991</v>
+        <v>6754018</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,13 +1958,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134964622</t>
+          <t>https://artportalen.se/Sighting/134955967</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134966813</v>
+        <v>134964622</v>
       </c>
       <c r="B14" t="n">
         <v>79411</v>
@@ -1989,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454443</v>
+        <v>454352</v>
       </c>
       <c r="R14" t="n">
-        <v>6754239</v>
+        <v>6753991</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2050,13 +2060,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134966813</t>
+          <t>https://artportalen.se/Sighting/134964622</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134968286</v>
+        <v>134966813</v>
       </c>
       <c r="B15" t="n">
         <v>79411</v>
@@ -2091,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454420</v>
+        <v>454443</v>
       </c>
       <c r="R15" t="n">
-        <v>6754156</v>
+        <v>6754239</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2152,54 +2162,54 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134968286</t>
+          <t>https://artportalen.se/Sighting/134966813</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122407517</v>
+        <v>134968286</v>
       </c>
       <c r="B16" t="n">
-        <v>80432</v>
+        <v>79411</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Långsisdammen, Dlr</t>
+          <t>Svarttjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
         <v>454420</v>
       </c>
       <c r="R16" t="n">
-        <v>6754420</v>
+        <v>6754156</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2223,17 +2233,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Lunglav på äldre sälg.</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2248,49 +2253,49 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122407517</t>
+          <t>https://artportalen.se/Sighting/134968286</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134969690</v>
+        <v>137404797</v>
       </c>
       <c r="B17" t="n">
-        <v>80526</v>
+        <v>79521</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2300,13 +2305,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454300</v>
+        <v>454480</v>
       </c>
       <c r="R17" t="n">
-        <v>6754194</v>
+        <v>6754482</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2330,12 +2335,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2350,70 +2365,65 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Via Caspar Ström</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134969690</t>
+          <t>https://artportalen.se/Sighting/137404797</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122409149</v>
+        <v>137404798</v>
       </c>
       <c r="B18" t="n">
-        <v>57953</v>
+        <v>79521</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Långsisdammen, Dlr</t>
+          <t>Svarttjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454455</v>
+        <v>454501</v>
       </c>
       <c r="R18" t="n">
-        <v>6754359</v>
+        <v>6754462</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2437,12 +2447,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2468,59 +2488,54 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122409149</t>
+          <t>https://artportalen.se/Sighting/137404798</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122410095</v>
+        <v>137404800</v>
       </c>
       <c r="B19" t="n">
-        <v>57953</v>
+        <v>79521</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Svarttjärnsberget, Svarttjärnsberget, Dlr</t>
+          <t>Svarttjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454463</v>
+        <v>454510</v>
       </c>
       <c r="R19" t="n">
-        <v>6754144</v>
+        <v>6754455</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2544,27 +2559,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack både färska och gamla</t>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2579,73 +2594,65 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122410095</t>
+          <t>https://artportalen.se/Sighting/137404800</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122410135</v>
+        <v>137404804</v>
       </c>
       <c r="B20" t="n">
-        <v>57141</v>
+        <v>79521</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Långsisdammen, Långsisdammen, Dlr</t>
+          <t>Svarttjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454406</v>
+        <v>454532</v>
       </c>
       <c r="R20" t="n">
-        <v>6754542</v>
+        <v>6754453</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2669,22 +2676,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2699,77 +2706,65 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122410135</t>
+          <t>https://artportalen.se/Sighting/137404804</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134971371</v>
+        <v>137404808</v>
       </c>
       <c r="B21" t="n">
-        <v>57167</v>
+        <v>79521</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Svarttjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454422</v>
+        <v>454493</v>
       </c>
       <c r="R21" t="n">
-        <v>6754214</v>
+        <v>6754419</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2793,12 +2788,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2813,70 +2818,65 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Samuel Holdar</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134971371</t>
+          <t>https://artportalen.se/Sighting/137404808</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122407785</v>
+        <v>137404810</v>
       </c>
       <c r="B22" t="n">
-        <v>5179</v>
+        <v>79521</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Långsisdammen, Långsisdammen, Dlr</t>
+          <t>Svarttjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454473</v>
+        <v>454504</v>
       </c>
       <c r="R22" t="n">
-        <v>6754360</v>
+        <v>6754403</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2900,22 +2900,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2930,49 +2930,49 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122407785</t>
+          <t>https://artportalen.se/Sighting/137404810</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134958556</v>
+        <v>137404814</v>
       </c>
       <c r="B23" t="n">
-        <v>5181</v>
+        <v>79521</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2982,13 +2982,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454356</v>
+        <v>454467</v>
       </c>
       <c r="R23" t="n">
-        <v>6754067</v>
+        <v>6754433</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3012,12 +3012,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3032,49 +3042,49 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Via Caspar Ström</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134958556</t>
+          <t>https://artportalen.se/Sighting/137404814</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134958985</v>
+        <v>137404816</v>
       </c>
       <c r="B24" t="n">
-        <v>99159</v>
+        <v>79521</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3084,13 +3094,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454284</v>
+        <v>454435</v>
       </c>
       <c r="R24" t="n">
-        <v>6754000</v>
+        <v>6754438</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3114,12 +3124,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3134,49 +3154,49 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Via Caspar Ström</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134958985</t>
+          <t>https://artportalen.se/Sighting/137404816</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134965357</v>
+        <v>137404818</v>
       </c>
       <c r="B25" t="n">
-        <v>99159</v>
+        <v>79521</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3186,13 +3206,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454287</v>
+        <v>454421</v>
       </c>
       <c r="R25" t="n">
-        <v>6754011</v>
+        <v>6754419</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3216,12 +3236,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3236,49 +3266,49 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Via Caspar Ström</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134965357</t>
+          <t>https://artportalen.se/Sighting/137404818</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134965543</v>
+        <v>137404820</v>
       </c>
       <c r="B26" t="n">
-        <v>99159</v>
+        <v>79521</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3288,13 +3318,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454318</v>
+        <v>454489</v>
       </c>
       <c r="R26" t="n">
-        <v>6753996</v>
+        <v>6754420</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3318,12 +3348,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3338,27 +3378,27 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Via Caspar Ström</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134965543</t>
+          <t>https://artportalen.se/Sighting/137404820</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134966608</v>
+        <v>137404822</v>
       </c>
       <c r="B27" t="n">
-        <v>99242</v>
+        <v>79521</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3366,41 +3406,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Svarttjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454330</v>
+        <v>454445</v>
       </c>
       <c r="R27" t="n">
-        <v>6754249</v>
+        <v>6754367</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3424,12 +3460,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3444,49 +3490,49 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Via Caspar Ström</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134966608</t>
+          <t>https://artportalen.se/Sighting/137404822</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134963152</v>
+        <v>137404823</v>
       </c>
       <c r="B28" t="n">
-        <v>98104</v>
+        <v>79521</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3496,13 +3542,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454243</v>
+        <v>454455</v>
       </c>
       <c r="R28" t="n">
-        <v>6754004</v>
+        <v>6754353</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3526,12 +3572,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3546,18 +3607,4928 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Via Caspar Ström</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137404823</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>137404826</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79521</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Svarttjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>454423</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6754354</v>
+      </c>
+      <c r="S29" t="n">
+        <v>6</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404826</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>137404829</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79521</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Svarttjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>454438</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6754273</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404829</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>137404831</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79521</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Svarttjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>454436</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6754243</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404831</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>137404832</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79521</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Svarttjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>454437</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6754246</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404832</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>137404835</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79521</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Svarttjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>454443</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6754209</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404835</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>137404840</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79521</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Svarttjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>454463</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6754118</v>
+      </c>
+      <c r="S34" t="n">
+        <v>8</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404840</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>137404841</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79521</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Svarttjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>454441</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6754107</v>
+      </c>
+      <c r="S35" t="n">
+        <v>8</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404841</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>137404843</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79521</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Svarttjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>454420</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6754132</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404843</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>137404844</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79521</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Svarttjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>454400</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6754105</v>
+      </c>
+      <c r="S37" t="n">
+        <v>7</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404844</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>137404845</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79521</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Svarttjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>454415</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6754090</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404845</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>137404847</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79521</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Svarttjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>454385</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6754041</v>
+      </c>
+      <c r="S39" t="n">
+        <v>8</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404847</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>137404848</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79521</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Svarttjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>454364</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6754076</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404848</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>137404851</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79521</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Svarttjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>454358</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6754187</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404851</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>137404852</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79521</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Svarttjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>454387</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6754187</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404852</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>122407517</v>
+      </c>
+      <c r="B43" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Långsisdammen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>454420</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6754420</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Lunglav på äldre sälg.</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122407517</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>134969690</v>
+      </c>
+      <c r="B44" t="n">
+        <v>80526</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Svarttjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>454300</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6754194</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134969690</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>137404796</v>
+      </c>
+      <c r="B45" t="n">
+        <v>80636</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Svarttjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>454480</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6754478</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404796</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>137404799</v>
+      </c>
+      <c r="B46" t="n">
+        <v>80636</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Svarttjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>454493</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6754473</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Riklikt på stammen</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404799</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>137404817</v>
+      </c>
+      <c r="B47" t="n">
+        <v>80636</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Svarttjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>454421</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6754419</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404817</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>122409149</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Långsisdammen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>454455</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6754359</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122409149</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>122410095</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Svarttjärnsberget, Svarttjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>454463</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6754144</v>
+      </c>
+      <c r="S49" t="n">
+        <v>9</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack både färska och gamla</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122410095</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>137404802</v>
+      </c>
+      <c r="B50" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Svarttjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>454551</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6754454</v>
+      </c>
+      <c r="S50" t="n">
+        <v>7</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404802</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>137404803</v>
+      </c>
+      <c r="B51" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Svarttjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>454537</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6754436</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404803</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>137404806</v>
+      </c>
+      <c r="B52" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Svarttjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>454514</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6754427</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Äldre och färska hack</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404806</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>137404833</v>
+      </c>
+      <c r="B53" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Svarttjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>454437</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6754246</v>
+      </c>
+      <c r="S53" t="n">
+        <v>9</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404833</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>137404834</v>
+      </c>
+      <c r="B54" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Svarttjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>454443</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6754209</v>
+      </c>
+      <c r="S54" t="n">
+        <v>12</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404834</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>137404836</v>
+      </c>
+      <c r="B55" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Svarttjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>454441</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6754211</v>
+      </c>
+      <c r="S55" t="n">
+        <v>7</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404836</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>137404837</v>
+      </c>
+      <c r="B56" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Svarttjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>454443</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6754213</v>
+      </c>
+      <c r="S56" t="n">
+        <v>11</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>På flera granstammar i närområet</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404837</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>137404839</v>
+      </c>
+      <c r="B57" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Svarttjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>454469</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6754138</v>
+      </c>
+      <c r="S57" t="n">
+        <v>6</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404839</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>137404842</v>
+      </c>
+      <c r="B58" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Svarttjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>454420</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6754132</v>
+      </c>
+      <c r="S58" t="n">
+        <v>8</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404842</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>137404849</v>
+      </c>
+      <c r="B59" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Svarttjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>454361</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6754082</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404849</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>137404850</v>
+      </c>
+      <c r="B60" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Svarttjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>454358</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6754187</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Bohål/bobygge. 2 och 2 5 meter upp,  4 till 4,5 cm i diameter</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404850</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>137404853</v>
+      </c>
+      <c r="B61" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Svarttjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>454365</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6754319</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404853</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>122410135</v>
+      </c>
+      <c r="B62" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Långsisdammen, Långsisdammen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>454406</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6754542</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122410135</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>134971371</v>
+      </c>
+      <c r="B63" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Svarttjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>454422</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6754214</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Samuel Holdar</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134971371</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>122407785</v>
+      </c>
+      <c r="B64" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Långsisdammen, Långsisdammen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>454473</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6754360</v>
+      </c>
+      <c r="S64" t="n">
+        <v>9</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122407785</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>134958556</v>
+      </c>
+      <c r="B65" t="n">
+        <v>5181</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Svarttjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>454356</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6754067</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134958556</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>137404812</v>
+      </c>
+      <c r="B66" t="n">
+        <v>58191</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Svarttjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>454470</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6754406</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404812</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>134958985</v>
+      </c>
+      <c r="B67" t="n">
+        <v>99159</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Svarttjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>454284</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6754000</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134958985</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>134965357</v>
+      </c>
+      <c r="B68" t="n">
+        <v>99159</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Svarttjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>454287</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6754011</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134965357</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>134965543</v>
+      </c>
+      <c r="B69" t="n">
+        <v>99159</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Svarttjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>454318</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6753996</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134965543</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>134966608</v>
+      </c>
+      <c r="B70" t="n">
+        <v>99242</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Svarttjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>454330</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6754249</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134966608</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>134963152</v>
+      </c>
+      <c r="B71" t="n">
+        <v>98104</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Svarttjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>454243</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6754004</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/134963152</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>137404815</v>
+      </c>
+      <c r="B72" t="n">
+        <v>98280</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Svarttjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>454448</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6754437</v>
+      </c>
+      <c r="S72" t="n">
+        <v>7</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404815</t>
         </is>
       </c>
     </row>
@@ -3590,6 +8561,50 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41952-2026 artfynd.xlsx
+++ b/artfynd/A 41952-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>137404838</v>
       </c>
       <c r="B4" t="n">
-        <v>92601</v>
+        <v>92613</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>137404797</v>
       </c>
       <c r="B17" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         <v>137404798</v>
       </c>
       <c r="B18" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>137404800</v>
       </c>
       <c r="B19" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>137404804</v>
       </c>
       <c r="B20" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>137404808</v>
       </c>
       <c r="B21" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>137404810</v>
       </c>
       <c r="B22" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>137404814</v>
       </c>
       <c r="B23" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>137404816</v>
       </c>
       <c r="B24" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>137404818</v>
       </c>
       <c r="B25" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>137404820</v>
       </c>
       <c r="B26" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         <v>137404822</v>
       </c>
       <c r="B27" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>137404823</v>
       </c>
       <c r="B28" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>137404826</v>
       </c>
       <c r="B29" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>137404829</v>
       </c>
       <c r="B30" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>137404831</v>
       </c>
       <c r="B31" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>137404832</v>
       </c>
       <c r="B32" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>137404835</v>
       </c>
       <c r="B33" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>137404840</v>
       </c>
       <c r="B34" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>137404841</v>
       </c>
       <c r="B35" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         <v>137404843</v>
       </c>
       <c r="B36" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         <v>137404844</v>
       </c>
       <c r="B37" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>137404845</v>
       </c>
       <c r="B38" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>137404847</v>
       </c>
       <c r="B39" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>137404848</v>
       </c>
       <c r="B40" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
         <v>137404851</v>
       </c>
       <c r="B41" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
         <v>137404852</v>
       </c>
       <c r="B42" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5404,7 +5404,7 @@
         <v>137404796</v>
       </c>
       <c r="B45" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
         <v>137404799</v>
       </c>
       <c r="B46" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>137404817</v>
       </c>
       <c r="B47" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -8425,7 +8425,7 @@
         <v>137404815</v>
       </c>
       <c r="B72" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 41952-2026 artfynd.xlsx
+++ b/artfynd/A 41952-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>137404838</v>
       </c>
       <c r="B4" t="n">
-        <v>92613</v>
+        <v>92614</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>137404797</v>
       </c>
       <c r="B17" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         <v>137404798</v>
       </c>
       <c r="B18" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>137404800</v>
       </c>
       <c r="B19" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>137404804</v>
       </c>
       <c r="B20" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>137404808</v>
       </c>
       <c r="B21" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>137404810</v>
       </c>
       <c r="B22" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>137404814</v>
       </c>
       <c r="B23" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>137404816</v>
       </c>
       <c r="B24" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>137404818</v>
       </c>
       <c r="B25" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>137404820</v>
       </c>
       <c r="B26" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         <v>137404822</v>
       </c>
       <c r="B27" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>137404823</v>
       </c>
       <c r="B28" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>137404826</v>
       </c>
       <c r="B29" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>137404829</v>
       </c>
       <c r="B30" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>137404831</v>
       </c>
       <c r="B31" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>137404832</v>
       </c>
       <c r="B32" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>137404835</v>
       </c>
       <c r="B33" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>137404840</v>
       </c>
       <c r="B34" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>137404841</v>
       </c>
       <c r="B35" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         <v>137404843</v>
       </c>
       <c r="B36" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         <v>137404844</v>
       </c>
       <c r="B37" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>137404845</v>
       </c>
       <c r="B38" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>137404847</v>
       </c>
       <c r="B39" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>137404848</v>
       </c>
       <c r="B40" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
         <v>137404851</v>
       </c>
       <c r="B41" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
         <v>137404852</v>
       </c>
       <c r="B42" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5404,7 +5404,7 @@
         <v>137404796</v>
       </c>
       <c r="B45" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
         <v>137404799</v>
       </c>
       <c r="B46" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>137404817</v>
       </c>
       <c r="B47" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -8425,7 +8425,7 @@
         <v>137404815</v>
       </c>
       <c r="B72" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 41952-2026 artfynd.xlsx
+++ b/artfynd/A 41952-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>137404838</v>
       </c>
       <c r="B4" t="n">
-        <v>92614</v>
+        <v>92617</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>137404797</v>
       </c>
       <c r="B17" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         <v>137404798</v>
       </c>
       <c r="B18" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>137404800</v>
       </c>
       <c r="B19" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>137404804</v>
       </c>
       <c r="B20" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>137404808</v>
       </c>
       <c r="B21" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>137404810</v>
       </c>
       <c r="B22" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>137404814</v>
       </c>
       <c r="B23" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>137404816</v>
       </c>
       <c r="B24" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>137404818</v>
       </c>
       <c r="B25" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>137404820</v>
       </c>
       <c r="B26" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         <v>137404822</v>
       </c>
       <c r="B27" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>137404823</v>
       </c>
       <c r="B28" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>137404826</v>
       </c>
       <c r="B29" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>137404829</v>
       </c>
       <c r="B30" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>137404831</v>
       </c>
       <c r="B31" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>137404832</v>
       </c>
       <c r="B32" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>137404835</v>
       </c>
       <c r="B33" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>137404840</v>
       </c>
       <c r="B34" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>137404841</v>
       </c>
       <c r="B35" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         <v>137404843</v>
       </c>
       <c r="B36" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         <v>137404844</v>
       </c>
       <c r="B37" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>137404845</v>
       </c>
       <c r="B38" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>137404847</v>
       </c>
       <c r="B39" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>137404848</v>
       </c>
       <c r="B40" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
         <v>137404851</v>
       </c>
       <c r="B41" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
         <v>137404852</v>
       </c>
       <c r="B42" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5404,7 +5404,7 @@
         <v>137404796</v>
       </c>
       <c r="B45" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
         <v>137404799</v>
       </c>
       <c r="B46" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>137404817</v>
       </c>
       <c r="B47" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -8425,7 +8425,7 @@
         <v>137404815</v>
       </c>
       <c r="B72" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 41952-2026 artfynd.xlsx
+++ b/artfynd/A 41952-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>137404838</v>
       </c>
       <c r="B4" t="n">
-        <v>92617</v>
+        <v>92621</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>137404797</v>
       </c>
       <c r="B17" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         <v>137404798</v>
       </c>
       <c r="B18" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>137404800</v>
       </c>
       <c r="B19" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>137404804</v>
       </c>
       <c r="B20" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>137404808</v>
       </c>
       <c r="B21" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>137404810</v>
       </c>
       <c r="B22" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>137404814</v>
       </c>
       <c r="B23" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>137404816</v>
       </c>
       <c r="B24" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>137404818</v>
       </c>
       <c r="B25" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>137404820</v>
       </c>
       <c r="B26" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         <v>137404822</v>
       </c>
       <c r="B27" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>137404823</v>
       </c>
       <c r="B28" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>137404826</v>
       </c>
       <c r="B29" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>137404829</v>
       </c>
       <c r="B30" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>137404831</v>
       </c>
       <c r="B31" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>137404832</v>
       </c>
       <c r="B32" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>137404835</v>
       </c>
       <c r="B33" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>137404840</v>
       </c>
       <c r="B34" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>137404841</v>
       </c>
       <c r="B35" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         <v>137404843</v>
       </c>
       <c r="B36" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         <v>137404844</v>
       </c>
       <c r="B37" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>137404845</v>
       </c>
       <c r="B38" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>137404847</v>
       </c>
       <c r="B39" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>137404848</v>
       </c>
       <c r="B40" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
         <v>137404851</v>
       </c>
       <c r="B41" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
         <v>137404852</v>
       </c>
       <c r="B42" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5404,7 +5404,7 @@
         <v>137404796</v>
       </c>
       <c r="B45" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
         <v>137404799</v>
       </c>
       <c r="B46" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>137404817</v>
       </c>
       <c r="B47" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         <v>137404802</v>
       </c>
       <c r="B50" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>137404803</v>
       </c>
       <c r="B51" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6200,7 +6200,7 @@
         <v>137404806</v>
       </c>
       <c r="B52" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>137404833</v>
       </c>
       <c r="B53" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>137404834</v>
       </c>
       <c r="B54" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6544,7 +6544,7 @@
         <v>137404836</v>
       </c>
       <c r="B55" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6657,7 +6657,7 @@
         <v>137404837</v>
       </c>
       <c r="B56" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
         <v>137404839</v>
       </c>
       <c r="B57" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
         <v>137404842</v>
       </c>
       <c r="B58" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>137404849</v>
       </c>
       <c r="B59" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>137404850</v>
       </c>
       <c r="B60" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         <v>137404853</v>
       </c>
       <c r="B61" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
         <v>137404812</v>
       </c>
       <c r="B66" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8425,7 +8425,7 @@
         <v>137404815</v>
       </c>
       <c r="B72" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
